--- a/assets/constructions/examples/ctd_mb3.xlsx
+++ b/assets/constructions/examples/ctd_mb3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT6"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,63 +659,104 @@
           <t>adintws</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VC4STBR0050T0200N10</t>
+          <t>E-TPM010.0205050-K2R0.5-d4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MITSUBISHI</t>
+          <t>AMATI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VC4STB</t>
+          <t>E-TPM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PMS</t>
-        </is>
-      </c>
+          <t>PMK</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0~-0.02</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>20.5</v>
       </c>
       <c r="K2" t="n">
         <v>0.5</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>20.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>20.5</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+        <v>20.5</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Super MG</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Super MG</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>MIRACLE</t>
+          <t>TISIN</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -727,10 +768,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -757,7 +798,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2020 / Mitsubishi Website</t>
+          <t>2023/Amati Форма Точности</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -773,79 +814,102 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-4</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>1149.46</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VCXBR0300T0100L051</t>
+          <t>EM863080</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MITSUBISHI</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VCXB</t>
+          <t>EM863</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MSH</t>
-        </is>
-      </c>
+          <t>KH</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/-0,02</t>
+          <t>0/-0,03</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>6.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>6.3</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="P3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>6.3</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Micro Grain Carbide</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>MIRACLE</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -857,22 +921,22 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Y3" t="n">
         <v>8</v>
       </c>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>6.5</v>
+      </c>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="n">
-        <v>7.11</v>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
         <v>30</v>
       </c>
@@ -891,7 +955,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2020 / Mitsubishi Website</t>
+          <t>2017 - YG1 - General catalogue</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -913,13 +977,24 @@
       <c r="AT3" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>KH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MP3XBR0100N016T15</t>
+          <t>VF3XBR0050T0054L030</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -929,7 +1004,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MP3XB</t>
+          <t>VF3XB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -939,39 +1014,47 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MNS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0/-0,02</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L4" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>(Al,Ti,Cr)N</t>
+          <t>IMPACT MIRACLE</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -983,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="Y4" t="n">
         <v>6</v>
@@ -991,16 +1074,18 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>2.54</v>
+        <v>1.81</v>
       </c>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>30</v>
+      </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1041,71 +1126,94 @@
           <t>WORKPIECE</t>
         </is>
       </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>PSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CBN2XLBR0050N025S04</t>
+          <t>4249 3.000</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MITSUBISHI</t>
+          <t>GUHRING</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CBN2XLB</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>PMKSH</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0/-0,01</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+          <t>h8</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>14</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="P5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>VHM</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Signum</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Werksnorm</t>
+        </is>
+      </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
@@ -1113,24 +1221,22 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="Y5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="n">
-        <v>15</v>
-      </c>
+      <c r="AE5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1147,12 +1253,12 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2020 / Mitsubishi Website</t>
+          <t>2019 GUHRING NEW LEVEL</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>CBN</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AQ5" t="b">
@@ -1163,75 +1269,86 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>HA-4</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9262280410</t>
+          <t>MP3XBR0050N016T10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HELION</t>
+          <t>MITSUBISHI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>92.6228</t>
+          <t>MP3XB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MNS</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>60</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>DEEP BLUE</t>
+          <t>(Al,Ti,Cr)N</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>HELION NORM</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
         <v>0</v>
       </c>
@@ -1239,14 +1356,16 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Y6" t="n">
         <v>6</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>1.42</v>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
@@ -1254,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1271,7 +1390,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2023/HELION_general_cataloge</t>
+          <t>2020 / Mitsubishi Website</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1293,6 +1412,17 @@
       <c r="AT6" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>PMNSH</t>
         </is>
       </c>
     </row>
